--- a/docs/experiments/nz-birdsong/capex_tinybox_entry.xlsx
+++ b/docs/experiments/nz-birdsong/capex_tinybox_entry.xlsx
@@ -527,8 +527,7 @@
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>School of Biological Sciences — shared core asset
-Azure (Shaw Lab)
-[Juni if co-applicant]</t>
+Jules (Shaw Lab)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
